--- a/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week07_12Oct.xlsx
+++ b/Planning/GROW/Progress_Tees_Valley_GROW_Weekly_Plan_Week07_12Oct.xlsx
@@ -1125,7 +1125,7 @@
     <row r="8" ht="45.75" customHeight="1" s="46">
       <c r="A8" s="54" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: BHM continues; Harvest window (tbc) — Grow PSHE W7's community-action pitch can adopt a harvest/food-bank action (strongest tie of the term).  Hate Crime Awareness Week — if this week, tie to the BV Rule of Law assembly.  EVIDENCE: planning boards + EFL: community/citizenship → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: BHM continues; Harvest window (tbc) — Grow PSHE W7's community-action pitch can adopt a harvest/food-bank action (strongest tie of the term).  Hate Crime Awareness Week — if this week, tie to the BV Rule of Law assembly.  EVIDENCE: planning boards + evidence platform: community/citizenship → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="55" t="n"/>
@@ -1332,7 +1332,7 @@
 Opportunities to review work and correct errors.
 Ongoing assessment through observation, discussion and completed tasks.
 Positive feedback and target-setting to support future progress.
-LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = mini-whiteboard show-me / re-do, verbal reply [VF, I] → Audience: name the corrected step back and tick the success criteria; [R] on an accurate re-do → EVIDENCE: photo of the practical proof + book note, same day [E: numeracy/vocational — daily evidence platform].</t>
         </is>
       </c>
       <c r="J11" s="63" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="I13" s="63" t="inlineStr">
         <is>
           <t>TA scaffolds the planning board; the HoS gives live feedback on the pitch and green-lights it; teacher keeps the action genuinely achievable in one week.
-LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to EFL, same day [E: PfA/citizenship/social enterprise — daily EFL].</t>
+LOOP [Feedback Policy]: Voice = campaign video / freeze-frame / card + verbal reply [VF] → Audience: name the strength back + one [NS]; listen to clips fully before tagging, then [R] → EVIDENCE: video/card photo to evidence platform, same day [E: PfA/citizenship/social enterprise — daily evidence platform].</t>
         </is>
       </c>
       <c r="J13" s="63" t="inlineStr">
